--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Single Row_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Single Row_report.xlsx
@@ -223,7 +223,7 @@
         <xdr:cNvPr id="3" name="Text Box 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{d8512e48-0a1c-4eb4-aaef-25e09ece098b}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{968a081c-fa48-4f28-83b0-b54bd890d2ab}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>

--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Single Row_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Single Row_report.xlsx
@@ -223,7 +223,7 @@
         <xdr:cNvPr id="3" name="Text Box 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{968a081c-fa48-4f28-83b0-b54bd890d2ab}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2bef6913-3870-41a8-aca6-29e9cfd09fa4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>

--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Single Row_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Single Row_report.xlsx
@@ -223,7 +223,7 @@
         <xdr:cNvPr id="3" name="Text Box 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2bef6913-3870-41a8-aca6-29e9cfd09fa4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{f1f3c365-196d-41da-951a-240d2c877b7c}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
